--- a/examples/ltd-latest/Companysecretary.xlsx
+++ b/examples/ltd-latest/Companysecretary.xlsx
@@ -720,7 +720,7 @@
       </c>
       <c r="G1" s="20" t="n">
         <f aca="false">SUM(G3:G19)</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H1" s="16"/>
       <c r="I1" s="16"/>
@@ -772,7 +772,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>27</v>

--- a/examples/ltd-latest/Companysecretary.xlsx
+++ b/examples/ltd-latest/Companysecretary.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="46">
   <si>
     <t xml:space="preserve">Minutes of Board Meeting held on</t>
   </si>
@@ -101,6 +101,9 @@
     <t xml:space="preserve">Number of shares sold</t>
   </si>
   <si>
+    <t xml:space="preserve">Carol Smith</t>
+  </si>
+  <si>
     <t xml:space="preserve">A0001</t>
   </si>
   <si>
@@ -110,12 +113,18 @@
     <t xml:space="preserve">Subscriber to Memorandum of Association</t>
   </si>
   <si>
+    <t xml:space="preserve">David Brown</t>
+  </si>
+  <si>
     <t xml:space="preserve">A0002</t>
   </si>
   <si>
     <t xml:space="preserve">Fully paid Ordinary Shares</t>
   </si>
   <si>
+    <t xml:space="preserve">Emma Wilson</t>
+  </si>
+  <si>
     <t xml:space="preserve">Date interest registered</t>
   </si>
   <si>
@@ -144,6 +153,15 @@
   </si>
   <si>
     <t xml:space="preserve">Date of the Board meeting at which transaction was confirmed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motor vehicles, being the company's delivery van</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NatWest Bank plc, 250 Bishopsgate, London EC2M 4AA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed charge securing a five year business loan</t>
   </si>
 </sst>
 </file>
@@ -511,7 +529,9 @@
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="6"/>
+      <c r="F2" s="6" t="n">
+        <v>46295</v>
+      </c>
       <c r="G2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -530,7 +550,9 @@
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="7"/>
+      <c r="E4" s="7" t="n">
+        <v>15000</v>
+      </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
     </row>
@@ -692,7 +714,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="18.66"/>
@@ -762,37 +784,63 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>43831</v>
+      </c>
       <c r="D3" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" s="22" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="23" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>44362</v>
+      </c>
       <c r="D4" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F4" s="22" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="23" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>44621</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -831,21 +879,21 @@
         <v>7</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D2" s="9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -865,7 +913,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="24" width="12.66"/>
@@ -879,22 +927,42 @@
   <sheetData>
     <row r="1" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>39</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="24" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="25" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="13" t="n">
+        <v>45163</v>
       </c>
     </row>
   </sheetData>

--- a/examples/ltd-latest/Companysecretary.xlsx
+++ b/examples/ltd-latest/Companysecretary.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="47">
   <si>
     <t xml:space="preserve">Minutes of Board Meeting held on</t>
   </si>
@@ -62,6 +62,12 @@
     <t xml:space="preserve">Date of resignation</t>
   </si>
   <si>
+    <t xml:space="preserve">Carol Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123 High Street, Manchester, M1 1AA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Director</t>
   </si>
   <si>
@@ -99,9 +105,6 @@
   </si>
   <si>
     <t xml:space="preserve">Number of shares sold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carol Smith</t>
   </si>
   <si>
     <t xml:space="preserve">A0001</t>
@@ -530,7 +533,7 @@
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="6" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="G2" s="3"/>
     </row>
@@ -681,20 +684,26 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="D2" s="9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D3" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -753,48 +762,48 @@
     </row>
     <row r="2" s="13" customFormat="true" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C3" s="14" t="n">
         <v>43831</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3" s="22" t="n">
         <v>1</v>
@@ -803,21 +812,21 @@
         <v>60</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="14" t="n">
         <v>44362</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" s="22" t="n">
         <v>1</v>
@@ -826,12 +835,12 @@
         <v>25</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>44621</v>
@@ -879,21 +888,30 @@
         <v>7</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="10" t="n">
+        <v>43831</v>
+      </c>
       <c r="D2" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -927,22 +945,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -950,16 +968,16 @@
         <v>45170</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="25" t="n">
         <v>30000</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F2" s="13" t="n">
         <v>45163</v>

--- a/examples/ltd-latest/Companysecretary.xlsx
+++ b/examples/ltd-latest/Companysecretary.xlsx
@@ -533,7 +533,7 @@
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="6" t="n">
-        <v>46326</v>
+        <v>46691</v>
       </c>
       <c r="G2" s="3"/>
     </row>
